--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD106F7-DC37-1043-BE4C-1171FB0D0EE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28F2B1-C283-614C-B261-1B66FC91B15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="1360" windowWidth="46240" windowHeight="26860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18060" yWindow="1940" windowWidth="46240" windowHeight="26860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Generelle plan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="119">
   <si>
     <t>Uge</t>
   </si>
@@ -115,9 +115,6 @@
     <t>Race week</t>
   </si>
   <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
     <t>Long 12 km</t>
   </si>
   <si>
@@ -127,22 +124,13 @@
     <t>Taper</t>
   </si>
   <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
     <t>Short tempo 10 km</t>
   </si>
   <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
     <t>Easy steady</t>
   </si>
   <si>
     <t>Short tempo 14 km</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
   </si>
   <si>
     <t>Exercise</t>
@@ -486,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -517,10 +505,12 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1059,7 +1049,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -1090,34 +1080,34 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>122</v>
-      </c>
       <c r="N1" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>4</v>
@@ -1131,7 +1121,7 @@
         <v>46118</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D2" s="9">
         <v>120</v>
@@ -1155,16 +1145,16 @@
         <v>11</v>
       </c>
       <c r="K2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="O2" s="8"/>
     </row>
@@ -1176,7 +1166,7 @@
         <v>46125</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D3" s="9">
         <v>130</v>
@@ -1200,7 +1190,7 @@
         <v>11</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L3" s="9" t="s">
         <v>10</v>
@@ -1209,7 +1199,7 @@
         <v>11</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O3" s="8"/>
     </row>
@@ -1221,7 +1211,7 @@
         <v>46132</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D4" s="9">
         <v>140</v>
@@ -1245,16 +1235,16 @@
         <v>11</v>
       </c>
       <c r="K4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="O4" s="8"/>
     </row>
@@ -1266,7 +1256,7 @@
         <v>46139</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D5" s="9">
         <v>150</v>
@@ -1290,16 +1280,16 @@
         <v>11</v>
       </c>
       <c r="K5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="O5" s="8"/>
     </row>
@@ -1307,17 +1297,17 @@
       <c r="A6">
         <v>19</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="17">
         <v>46146</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2">
         <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
@@ -1326,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>10</v>
@@ -1335,7 +1325,7 @@
         <v>11</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>19</v>
@@ -1344,14 +1334,14 @@
         <v>20</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>20</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="18">
         <v>46153</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1379,16 +1369,16 @@
         <v>11</v>
       </c>
       <c r="K7" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="O7" s="6"/>
     </row>
@@ -1396,11 +1386,11 @@
       <c r="A8" s="6">
         <v>21</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="18">
         <v>46160</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D8" s="7">
         <v>145</v>
@@ -1424,7 +1414,7 @@
         <v>11</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>10</v>
@@ -1433,7 +1423,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>15</v>
@@ -1443,7 +1433,7 @@
       <c r="A9" s="6">
         <v>22</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="18">
         <v>46167</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1471,7 +1461,7 @@
         <v>11</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L9" s="7" t="s">
         <v>10</v>
@@ -1480,7 +1470,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O9" s="6"/>
     </row>
@@ -1488,7 +1478,7 @@
       <c r="A10" s="6">
         <v>23</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <v>46174</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1516,16 +1506,16 @@
         <v>11</v>
       </c>
       <c r="K10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="O10" s="6"/>
     </row>
@@ -1533,17 +1523,17 @@
       <c r="A11">
         <v>24</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="17">
         <v>46181</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D11" s="2">
         <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>10</v>
@@ -1552,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>10</v>
@@ -1561,7 +1551,7 @@
         <v>11</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>19</v>
@@ -1570,18 +1560,18 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>25</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>46188</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D12" s="11">
         <v>145</v>
@@ -1605,16 +1595,16 @@
         <v>11</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="O12" s="10"/>
     </row>
@@ -1622,11 +1612,11 @@
       <c r="A13" s="10">
         <v>26</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>46195</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D13" s="11">
         <v>155</v>
@@ -1650,16 +1640,16 @@
         <v>11</v>
       </c>
       <c r="K13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N13" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="O13" s="10"/>
     </row>
@@ -1667,11 +1657,11 @@
       <c r="A14" s="10">
         <v>27</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <v>46202</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D14" s="11">
         <v>150</v>
@@ -1695,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>10</v>
@@ -1704,7 +1694,7 @@
         <v>11</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O14" s="10" t="s">
         <v>16</v>
@@ -1714,11 +1704,11 @@
       <c r="A15" s="10">
         <v>28</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <v>46209</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D15" s="11">
         <v>140</v>
@@ -1742,16 +1732,16 @@
         <v>11</v>
       </c>
       <c r="K15" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="O15" s="10"/>
     </row>
@@ -1759,17 +1749,17 @@
       <c r="A16">
         <v>29</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="17">
         <v>46216</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2">
         <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
@@ -1787,7 +1777,7 @@
         <v>20</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>19</v>
@@ -1796,7 +1786,7 @@
         <v>20</v>
       </c>
       <c r="N16" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
@@ -1806,11 +1796,11 @@
       <c r="A17" s="12">
         <v>30</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>46223</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D17" s="13">
         <v>135</v>
@@ -1834,7 +1824,7 @@
         <v>20</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>10</v>
@@ -1843,7 +1833,7 @@
         <v>11</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O17" s="12" t="s">
         <v>21</v>
@@ -1853,11 +1843,11 @@
       <c r="A18" s="12">
         <v>31</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>46230</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="13">
         <v>140</v>
@@ -1881,7 +1871,7 @@
         <v>20</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>10</v>
@@ -1890,7 +1880,7 @@
         <v>11</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O18" s="12" t="s">
         <v>21</v>
@@ -1900,11 +1890,11 @@
       <c r="A19" s="12">
         <v>32</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>46237</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D19" s="13">
         <v>150</v>
@@ -1928,16 +1918,16 @@
         <v>11</v>
       </c>
       <c r="K19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="O19" s="12"/>
     </row>
@@ -1945,17 +1935,17 @@
       <c r="A20">
         <v>33</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="17">
         <v>46244</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2">
         <v>110</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1964,7 +1954,7 @@
         <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>10</v>
@@ -1973,7 +1963,7 @@
         <v>11</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>19</v>
@@ -1982,24 +1972,24 @@
         <v>20</v>
       </c>
       <c r="N20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="14">
         <v>34</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>35</v>
+      <c r="B21" s="21">
+        <v>46251</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="15">
         <v>90</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F21" s="15" t="s">
         <v>7</v>
@@ -2008,7 +1998,7 @@
         <v>8</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>19</v>
@@ -2017,7 +2007,7 @@
         <v>20</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L21" s="15" t="s">
         <v>10</v>
@@ -2026,7 +2016,7 @@
         <v>11</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O21" s="14"/>
     </row>
@@ -2034,17 +2024,17 @@
       <c r="A22" s="14">
         <v>35</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>32</v>
+      <c r="B22" s="21">
+        <v>46258</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="15">
         <v>70</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>7</v>
@@ -2062,7 +2052,7 @@
         <v>20</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L22" s="15" t="s">
         <v>10</v>
@@ -2071,7 +2061,7 @@
         <v>11</v>
       </c>
       <c r="N22" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O22" s="14"/>
     </row>
@@ -2079,17 +2069,17 @@
       <c r="A23" s="14">
         <v>36</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>30</v>
+      <c r="B23" s="21">
+        <v>46265</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="15">
         <v>50</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" s="15" t="s">
         <v>19</v>
@@ -2107,7 +2097,7 @@
         <v>8</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L23" s="15" t="s">
         <v>19</v>
@@ -2116,7 +2106,7 @@
         <v>20</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O23" s="14"/>
     </row>
@@ -2124,8 +2114,8 @@
       <c r="A24">
         <v>37</v>
       </c>
-      <c r="B24" t="s">
-        <v>26</v>
+      <c r="B24" s="17">
+        <v>46272</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -2201,42 +2191,42 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B2">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2">
@@ -2246,44 +2236,44 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B3">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B4">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B5">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -2294,48 +2284,48 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B6">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B7">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F7" s="2"/>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B8">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H8">
         <f>H2-H5</f>
@@ -2344,7 +2334,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -2355,7 +2345,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -2366,7 +2356,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.2">
@@ -2377,7 +2367,7 @@
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H19" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.2">
@@ -2388,7 +2378,7 @@
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="8:8" x14ac:dyDescent="0.2">
@@ -2409,152 +2399,152 @@
   <sheetData>
     <row r="2" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C28F2B1-C283-614C-B261-1B66FC91B15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7907C620-7711-7649-86FE-0F56A861F477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18060" yWindow="1940" windowWidth="46240" windowHeight="26860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Generelle plan" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="120">
   <si>
     <t>Uge</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>BPM Long</t>
+  </si>
+  <si>
+    <t>15,3</t>
   </si>
 </sst>
 </file>
@@ -2222,6 +2225,9 @@
       <c r="B2">
         <v>15</v>
       </c>
+      <c r="C2" t="s">
+        <v>119</v>
+      </c>
       <c r="D2" t="s">
         <v>110</v>
       </c>

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7907C620-7711-7649-86FE-0F56A861F477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7FB759-15CC-D94C-B6B0-29D211D4BFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="119">
   <si>
     <t>Uge</t>
   </si>
@@ -392,9 +392,6 @@
   </si>
   <si>
     <t>BPM Long</t>
-  </si>
-  <si>
-    <t>15,3</t>
   </si>
 </sst>
 </file>
@@ -2225,8 +2222,8 @@
       <c r="B2">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>119</v>
+      <c r="C2">
+        <v>15.3</v>
       </c>
       <c r="D2" t="s">
         <v>110</v>
@@ -2357,7 +2354,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H14">
         <f>SUM(C2:C8)</f>
-        <v>0</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7FB759-15CC-D94C-B6B0-29D211D4BFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC928EEA-43E4-9D4E-8D8F-12C9B1C99CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2244,6 +2244,9 @@
       <c r="B3">
         <v>20</v>
       </c>
+      <c r="C3">
+        <v>22.94</v>
+      </c>
       <c r="D3" t="s">
         <v>101</v>
       </c>
@@ -2354,7 +2357,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H14">
         <f>SUM(C2:C8)</f>
-        <v>15.3</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -2399,6 +2402,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49AAF96-1551-A741-AB0A-EC1D8F9ABE69}">
   <dimension ref="D2:G14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="26.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D2" t="s">

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC928EEA-43E4-9D4E-8D8F-12C9B1C99CF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC00E7E1-CDB1-424D-BC8F-F6F8AA82BC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2260,6 +2260,9 @@
       <c r="B4">
         <v>12</v>
       </c>
+      <c r="C4">
+        <v>13.1</v>
+      </c>
       <c r="D4" t="s">
         <v>110</v>
       </c>
@@ -2357,7 +2360,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H14">
         <f>SUM(C2:C8)</f>
-        <v>38.24</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC00E7E1-CDB1-424D-BC8F-F6F8AA82BC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B5725-9D5E-924D-A919-B29E18D6FE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="1800" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Generelle plan" sheetId="1" r:id="rId1"/>
@@ -2281,6 +2281,9 @@
       <c r="B5">
         <v>16</v>
       </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
       <c r="D5" t="s">
         <v>102</v>
       </c>
@@ -2360,7 +2363,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H14">
         <f>SUM(C2:C8)</f>
-        <v>51.34</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B5725-9D5E-924D-A919-B29E18D6FE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A9C144-3537-C640-9B2A-4DD220740ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1800" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="120">
   <si>
     <t>Uge</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>BPM Long</t>
+  </si>
+  <si>
+    <t>B2B</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CACA1-AEAF-0543-B4E8-ABA117A45B7C}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -2220,21 +2223,21 @@
         <v>90</v>
       </c>
       <c r="B2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>109</v>
       </c>
       <c r="F2" s="2"/>
       <c r="H2">
-        <f>'Generelle plan'!D2</f>
-        <v>120</v>
+        <f>'Generelle plan'!D7</f>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -2242,13 +2245,13 @@
         <v>91</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C3">
-        <v>22.94</v>
+        <v>19.3</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -2258,10 +2261,10 @@
         <v>92</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>13.1</v>
+        <v>7.2</v>
       </c>
       <c r="D4" t="s">
         <v>110</v>
@@ -2279,10 +2282,10 @@
         <v>93</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>27.66</v>
       </c>
       <c r="D5" t="s">
         <v>102</v>
@@ -2291,7 +2294,7 @@
       <c r="F5" s="2"/>
       <c r="H5">
         <f>SUM(SUMIF(D2:D8,{"Key1","Key2","Long","B2B"},B2:B8))</f>
-        <v>66</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -2299,7 +2302,10 @@
         <v>94</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>12.5</v>
       </c>
       <c r="D6" t="s">
         <v>110</v>
@@ -2312,10 +2318,10 @@
         <v>95</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>109</v>
@@ -2330,10 +2336,10 @@
         <v>97</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
@@ -2341,7 +2347,7 @@
       </c>
       <c r="H8">
         <f>H2-H5</f>
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -2352,7 +2358,7 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H11">
         <f>SUM(B2:B8)</f>
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -2363,7 +2369,7 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="H14">
         <f>SUM(C2:C8)</f>
-        <v>59.34</v>
+        <v>81.86</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -2371,33 +2377,55 @@
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H17" t="str">
         <f>IF(H11&gt;H2+10,"⚠️ Overload",IF(H11&lt;H2-15,"⚠️ For lav volumen","OK"))</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H19" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H20">
         <f>COUNTIF(E2:E8,"Ja")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H23">
         <f>COUNTIF(F2:F8,"Ja")</f>
         <v>2</v>
       </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="7"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A9C144-3537-C640-9B2A-4DD220740ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ADD3AF-BA82-A84D-A1B1-D17C4331AF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1800" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2254,7 +2254,9 @@
         <v>110</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -2269,8 +2271,7 @@
       <c r="D4" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>109</v>
       </c>
       <c r="H4" t="s">
@@ -2311,7 +2312,9 @@
         <v>110</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -2323,9 +2326,6 @@
       <c r="D7" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="F7" s="2"/>
       <c r="H7" t="s">
         <v>96</v>
@@ -2342,9 +2342,6 @@
         <v>119</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="H8">
         <f>H2-H5</f>
         <v>34</v>
@@ -2401,7 +2398,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H23">
-        <f>COUNTIF(F2:F8,"Ja")</f>
+        <f>COUNTIF(F2:F7,"Ja")</f>
         <v>2</v>
       </c>
     </row>

--- a/data/training_plan.xlsx
+++ b/data/training_plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fs61oo/Documents/GitHub/rohderunning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ADD3AF-BA82-A84D-A1B1-D17C4331AF0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EC04F6-3982-4849-AC53-69BD6ECA2E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1800" windowWidth="41120" windowHeight="25800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="120">
   <si>
     <t>Uge</t>
   </si>
@@ -2403,21 +2403,11 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="6"/>
       <c r="I32" s="7"/>
